--- a/Data Analysis/HLOOKUP.xlsx
+++ b/Data Analysis/HLOOKUP.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
   <si>
     <t>Product_ID</t>
   </si>
@@ -112,6 +112,51 @@
   </si>
   <si>
     <t>Mechanical Keyboard</t>
+  </si>
+  <si>
+    <t>Order_Id</t>
+  </si>
+  <si>
+    <t>Product_Id</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>0-001</t>
+  </si>
+  <si>
+    <t>0-002</t>
+  </si>
+  <si>
+    <t>0-003</t>
+  </si>
+  <si>
+    <t>0-004</t>
+  </si>
+  <si>
+    <t>0-005</t>
+  </si>
+  <si>
+    <t>0-006</t>
+  </si>
+  <si>
+    <t>0-007</t>
+  </si>
+  <si>
+    <t>0-008</t>
+  </si>
+  <si>
+    <t>0-009</t>
+  </si>
+  <si>
+    <t>P999</t>
+  </si>
+  <si>
+    <t>0-010</t>
+  </si>
+  <si>
+    <t>P821</t>
   </si>
 </sst>
 </file>
@@ -121,7 +166,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,6 +181,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -145,7 +198,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -154,42 +207,61 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="thin">
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -201,7 +273,9 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -214,49 +288,75 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -267,36 +367,6 @@
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="medium">
@@ -314,40 +384,71 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -629,167 +730,306 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:E12"/>
+  <dimension ref="B3:L16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.90625" customWidth="1"/>
-    <col min="3" max="3" width="19.7265625" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="11" max="11" width="11.26953125" customWidth="1"/>
+    <col min="12" max="12" width="10.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="7" t="s">
+    <row r="3" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B4" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B5" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="C5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="B6" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="C6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="12" t="s">
         <v>3</v>
       </c>
+      <c r="C7" s="9">
+        <v>24.99</v>
+      </c>
+      <c r="D7" s="6">
+        <v>49.99</v>
+      </c>
+      <c r="E7" s="6">
+        <v>79.989999999999995</v>
+      </c>
+      <c r="F7" s="6">
+        <v>12.5</v>
+      </c>
+      <c r="G7" s="6">
+        <v>149.99</v>
+      </c>
+      <c r="H7" s="6">
+        <v>39.99</v>
+      </c>
+      <c r="I7" s="6">
+        <v>29.99</v>
+      </c>
+      <c r="J7" s="6">
+        <v>18.75</v>
+      </c>
+      <c r="K7" s="6">
+        <v>14.99</v>
+      </c>
+      <c r="L7" s="2">
+        <v>89.99</v>
+      </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B3" s="9" t="s">
+    <row r="9" spans="2:12" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B13" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="L13" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B14" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="E14" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="L14" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B15" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="22">
+        <v>2</v>
+      </c>
+      <c r="D15" s="16">
+        <v>4</v>
+      </c>
+      <c r="E15" s="16">
+        <v>1</v>
+      </c>
+      <c r="F15" s="16">
+        <v>9</v>
+      </c>
+      <c r="G15" s="16">
         <v>6</v>
       </c>
-      <c r="E3" s="2">
+      <c r="H15" s="16">
+        <v>4</v>
+      </c>
+      <c r="I15" s="16">
+        <v>7</v>
+      </c>
+      <c r="J15" s="16">
+        <v>2</v>
+      </c>
+      <c r="K15" s="16">
+        <v>7</v>
+      </c>
+      <c r="L15" s="19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="23">
+        <f>HLOOKUP(C14,$B$4:$L$7,4,FALSE)</f>
+        <v>79.989999999999995</v>
+      </c>
+      <c r="D16" s="23">
+        <f t="shared" ref="D16:L16" si="0">HLOOKUP(D14,$B$4:$L$7,4,FALSE)</f>
         <v>24.99</v>
       </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B4" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="E16" s="23">
+        <f t="shared" si="0"/>
+        <v>24.99</v>
+      </c>
+      <c r="F16" s="23">
+        <f t="shared" si="0"/>
         <v>49.99</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B5" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="G16" s="23">
+        <f t="shared" si="0"/>
         <v>79.989999999999995</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B6" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="4">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B7" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="4">
-        <v>149.99</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B8" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="4">
-        <v>39.99</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="H16" s="23">
+        <f t="shared" si="0"/>
         <v>29.99</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B10" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="4">
-        <v>18.75</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B11" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="4">
+      <c r="I16" s="23">
+        <f t="shared" si="0"/>
         <v>14.99</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="6">
-        <v>89.99</v>
+      <c r="J16" s="23">
+        <f t="shared" si="0"/>
+        <v>24.99</v>
+      </c>
+      <c r="K16" s="23" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="L16" s="23" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
